--- a/powercup.xlsx
+++ b/powercup.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D64FCE8-FA2F-4D3D-BE2F-6E028725C641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F30824-CD21-4939-B044-C820EC22F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1164" windowWidth="23040" windowHeight="12240" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
   </bookViews>
   <sheets>
     <sheet name="powercup" sheetId="1" r:id="rId1"/>
-    <sheet name="2025" sheetId="8" r:id="rId2"/>
-    <sheet name="2024" sheetId="7" r:id="rId3"/>
-    <sheet name="2023" sheetId="6" r:id="rId4"/>
-    <sheet name="2022" sheetId="5" r:id="rId5"/>
-    <sheet name="2021" sheetId="4" r:id="rId6"/>
-    <sheet name="2019" sheetId="3" r:id="rId7"/>
-    <sheet name="2018" sheetId="2" r:id="rId8"/>
-    <sheet name="2017" sheetId="9" r:id="rId9"/>
-    <sheet name="2016" sheetId="10" r:id="rId10"/>
+    <sheet name="2026" sheetId="11" r:id="rId2"/>
+    <sheet name="2025" sheetId="8" r:id="rId3"/>
+    <sheet name="2024" sheetId="7" r:id="rId4"/>
+    <sheet name="2023" sheetId="6" r:id="rId5"/>
+    <sheet name="2022" sheetId="5" r:id="rId6"/>
+    <sheet name="2021" sheetId="4" r:id="rId7"/>
+    <sheet name="2019" sheetId="3" r:id="rId8"/>
+    <sheet name="2018" sheetId="2" r:id="rId9"/>
+    <sheet name="2017" sheetId="9" r:id="rId10"/>
+    <sheet name="2016" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="362">
   <si>
     <t>sarja</t>
   </si>
@@ -203,9 +204,6 @@
     <t>Sijoitus 13</t>
   </si>
   <si>
-    <t>B-super/Kajastus</t>
-  </si>
-  <si>
     <t>OsVa Sudet</t>
   </si>
   <si>
@@ -1116,6 +1114,24 @@
   </si>
   <si>
     <t>sijoitus 14</t>
+  </si>
+  <si>
+    <t>B-tsemppi</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B-tsemppi A-V</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>A Jankko</t>
+  </si>
+  <si>
+    <t>B-super/Kajastus/I-V</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1186,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1186,6 +1202,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1297,7 +1319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1358,7 +1380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1379,10 +1401,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1408,6 +1430,18 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1723,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262665A1-DD70-4A77-B568-0DD7B9717A2E}">
-  <dimension ref="A1:P123"/>
+  <dimension ref="A1:P125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="10.77734375" customWidth="1"/>
@@ -1733,31 +1767,31 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>273</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>274</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
@@ -1769,10 +1803,10 @@
     </row>
     <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>276</v>
       </c>
       <c r="C2" s="13">
         <f t="shared" ref="C2:C8" si="0">SUM(D2:F2)</f>
@@ -1848,7 +1882,7 @@
         <v>39</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C4" s="13">
         <f t="shared" si="0"/>
@@ -1885,7 +1919,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" si="0"/>
@@ -1911,16 +1945,16 @@
         <v>1379</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" s="13">
         <f t="shared" si="0"/>
@@ -1946,13 +1980,13 @@
         <v>1340</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B7" s="10">
         <v>2017.2025000000001</v>
@@ -1987,10 +2021,10 @@
     </row>
     <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>52</v>
+        <v>361</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C8" s="13">
         <f t="shared" si="0"/>
@@ -2025,16 +2059,20 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="41" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2043,43 +2081,73 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12">
-        <f t="shared" ref="C10:H10" si="1">SUM(C2:C9)</f>
+      <c r="A10" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="12">
+        <f t="shared" ref="C12:H12" si="1">SUM(C2:C11)</f>
         <v>162</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D12" s="12">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E12" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F12" s="12">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G12" s="12">
         <f t="shared" si="1"/>
         <v>7997</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H12" s="12">
         <f t="shared" si="1"/>
         <v>7534</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I12" s="13"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
@@ -2092,27 +2160,19 @@
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
     </row>
     <row r="17" spans="7:16" x14ac:dyDescent="0.3">
-      <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="7:16" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="7:16" x14ac:dyDescent="0.3">
       <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
+      <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -2126,17 +2186,16 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="7:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="7:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="2"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="7:16" x14ac:dyDescent="0.3">
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2144,28 +2203,39 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="7:16" x14ac:dyDescent="0.3">
+      <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-      <c r="F38" s="3"/>
+    <row r="23" spans="7:16" x14ac:dyDescent="0.3">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="7:16" x14ac:dyDescent="0.3">
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
@@ -2196,72 +2266,72 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
-      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
-      <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E63" s="3"/>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="4"/>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="4"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E65" s="3"/>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" s="4"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" s="4"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" s="4"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" s="4"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" s="4"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" s="4"/>
-      <c r="F80" s="5"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B81" s="4"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B82" s="4"/>
+      <c r="F82" s="5"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B83" s="4"/>
@@ -2283,14 +2353,13 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B89" s="4"/>
-      <c r="F89" s="5"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B90" s="4"/>
-      <c r="F90" s="5"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B91" s="4"/>
+      <c r="F91" s="5"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B92" s="4"/>
@@ -2298,10 +2367,10 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B93" s="4"/>
-      <c r="F93" s="5"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B94" s="4"/>
+      <c r="F94" s="5"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B95" s="4"/>
@@ -2309,10 +2378,10 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B96" s="4"/>
-      <c r="F96" s="5"/>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B97" s="4"/>
+      <c r="F97" s="5"/>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B98" s="4"/>
@@ -2320,7 +2389,6 @@
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B99" s="4"/>
-      <c r="F99" s="5"/>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B100" s="4"/>
@@ -2332,6 +2400,7 @@
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B102" s="4"/>
+      <c r="F102" s="5"/>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B103" s="4"/>
@@ -2339,7 +2408,6 @@
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B104" s="4"/>
-      <c r="F104" s="5"/>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B105" s="4"/>
@@ -2347,6 +2415,7 @@
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B106" s="4"/>
+      <c r="F106" s="5"/>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B107" s="4"/>
@@ -2354,7 +2423,6 @@
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B108" s="4"/>
-      <c r="F108" s="5"/>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B109" s="4"/>
@@ -2366,6 +2434,7 @@
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B111" s="4"/>
+      <c r="F111" s="5"/>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B112" s="4"/>
@@ -2373,7 +2442,6 @@
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B113" s="4"/>
-      <c r="F113" s="5"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B114" s="4"/>
@@ -2381,6 +2449,7 @@
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B115" s="4"/>
+      <c r="F115" s="5"/>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B116" s="4"/>
@@ -2388,27 +2457,34 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B117" s="4"/>
-      <c r="F117" s="5"/>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B118" s="4"/>
+      <c r="F118" s="5"/>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B119" s="4"/>
+      <c r="F119" s="5"/>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B120" s="4"/>
-      <c r="F120" s="5"/>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B121" s="4"/>
-      <c r="F121" s="5"/>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B122" s="4"/>
+      <c r="F122" s="5"/>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B123" s="4"/>
+      <c r="F123" s="5"/>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B124" s="4"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B125" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2417,6 +2493,484 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A76EE42-D30F-444C-A57D-B2E37EAE4ABE}">
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="18" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11">
+        <v>2</v>
+      </c>
+      <c r="I1" s="11">
+        <v>1</v>
+      </c>
+      <c r="J1" s="11">
+        <v>0</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="19"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="38">
+        <v>42894</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="H2" s="13">
+        <v>1</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13">
+        <v>54</v>
+      </c>
+      <c r="L2" s="13">
+        <v>54</v>
+      </c>
+      <c r="M2" s="13"/>
+      <c r="N2" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="O2" s="13">
+        <f>SUM(H2:H11)*2</f>
+        <v>12</v>
+      </c>
+      <c r="P2" s="13">
+        <f>SUM(J2:J11)*2</f>
+        <v>8</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>SUM(K2:K11)</f>
+        <v>501</v>
+      </c>
+      <c r="R2" s="13">
+        <f>SUM(L2:L11)</f>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="37">
+        <v>42894</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8">
+        <v>32</v>
+      </c>
+      <c r="L3" s="8">
+        <v>50</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+    </row>
+    <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B4" s="38">
+        <v>42895</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13">
+        <v>1</v>
+      </c>
+      <c r="K4" s="13">
+        <v>40</v>
+      </c>
+      <c r="L4" s="13">
+        <v>50</v>
+      </c>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+    </row>
+    <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" s="37">
+        <v>42895</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8">
+        <v>51</v>
+      </c>
+      <c r="L5" s="8">
+        <v>38</v>
+      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+    </row>
+    <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="38">
+        <v>42895</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="H6" s="13">
+        <v>1</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13">
+        <v>50</v>
+      </c>
+      <c r="L6" s="13">
+        <v>43</v>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+    </row>
+    <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="37">
+        <v>42896</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8">
+        <v>50</v>
+      </c>
+      <c r="L7" s="8">
+        <v>36</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="38">
+        <v>42896</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="13">
+        <v>54</v>
+      </c>
+      <c r="L8" s="13">
+        <v>62</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+    </row>
+    <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" s="37">
+        <v>42896</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8">
+        <v>54</v>
+      </c>
+      <c r="L9" s="8">
+        <v>55</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="38">
+        <v>42897</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="H10" s="13">
+        <v>1</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13">
+        <v>61</v>
+      </c>
+      <c r="L10" s="13">
+        <v>49</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" s="37">
+        <v>42897</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
+        <v>55</v>
+      </c>
+      <c r="L11" s="8">
+        <v>49</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8196E2E4-C0F1-4E18-ACB3-0642A8C11EF5}">
   <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2474,7 +3028,7 @@
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B2" s="40">
         <v>42530</v>
@@ -2486,13 +3040,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H2" s="13">
         <v>1</v>
@@ -2507,7 +3061,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H10)*2</f>
@@ -2528,7 +3082,7 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B3" s="39">
         <v>42531</v>
@@ -2540,13 +3094,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>43</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -2568,7 +3122,7 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="40">
         <v>42531</v>
@@ -2580,13 +3134,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
@@ -2608,7 +3162,7 @@
     </row>
     <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B5" s="39">
         <v>42531</v>
@@ -2620,13 +3174,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -2646,7 +3200,7 @@
     </row>
     <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B6" s="40">
         <v>42532</v>
@@ -2658,13 +3212,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -2686,7 +3240,7 @@
     </row>
     <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B7" s="39">
         <v>42532</v>
@@ -2698,13 +3252,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -2726,7 +3280,7 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B8" s="40">
         <v>42532</v>
@@ -2738,13 +3292,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -2766,7 +3320,7 @@
     </row>
     <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B9" s="39">
         <v>42533</v>
@@ -2778,13 +3332,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
@@ -2806,7 +3360,7 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B10" s="40">
         <v>42533</v>
@@ -2824,7 +3378,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
@@ -2838,7 +3392,7 @@
         <v>50</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -2864,6 +3418,620 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA206A6D-3A2A-4A37-924D-F0159A1B20B0}">
+  <dimension ref="A1:R32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="18" width="10.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11">
+        <v>2</v>
+      </c>
+      <c r="I1" s="11">
+        <v>1</v>
+      </c>
+      <c r="J1" s="11">
+        <v>0</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="19"/>
+      <c r="N1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="O2" s="13">
+        <f>SUM(H2:H13)*2</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="13">
+        <f>SUM(J2:J13)*2</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>SUM(K2:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="13">
+        <f>SUM(L2:L13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="O3" s="8">
+        <f>SUM(H14:H25)*2</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <f>SUM(J14:J25)*2</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="8">
+        <f>SUM(K14:K25)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <f>SUM(L14:L25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="13"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="O5" s="8">
+        <f>SUM(O2:O3)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <f>SUM(P2:P3)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <f>SUM(Q2:Q3)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <f>SUM(R2:R3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="13"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="13"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="13"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B26" s="4"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B29" s="4"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B30" s="4"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B32" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8448F5B0-5C6D-4A96-8BFA-865C4CD93547}">
   <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2923,7 +4091,7 @@
     </row>
     <row r="2" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B2" s="20">
         <v>45813</v>
@@ -2932,16 +4100,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H2" s="13">
         <v>1</v>
@@ -2956,7 +4124,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H13)*2</f>
@@ -2977,7 +4145,7 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B3" s="16">
         <v>45813</v>
@@ -2986,16 +4154,16 @@
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>43</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -3010,7 +4178,7 @@
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H14:H25)*2</f>
@@ -3031,7 +4199,7 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B4" s="20">
         <v>45814</v>
@@ -3040,16 +4208,16 @@
         <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
@@ -3071,7 +4239,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B5" s="16">
         <v>45814</v>
@@ -3080,16 +4248,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -3104,7 +4272,7 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O5" s="8">
         <f>SUM(O2:O3)</f>
@@ -3125,7 +4293,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B6" s="20">
         <v>45814</v>
@@ -3134,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
@@ -3165,7 +4333,7 @@
     </row>
     <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B7" s="16">
         <v>45814</v>
@@ -3174,16 +4342,16 @@
         <v>17</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -3205,7 +4373,7 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B8" s="20">
         <v>45815</v>
@@ -3214,16 +4382,16 @@
         <v>26</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -3245,7 +4413,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B9" s="16">
         <v>45815</v>
@@ -3254,16 +4422,16 @@
         <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
@@ -3285,7 +4453,7 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B10" s="20">
         <v>45815</v>
@@ -3294,16 +4462,16 @@
         <v>26</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H10" s="13">
         <v>1</v>
@@ -3325,7 +4493,7 @@
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B11" s="16">
         <v>45815</v>
@@ -3334,7 +4502,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>9</v>
@@ -3343,7 +4511,7 @@
         <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -3365,7 +4533,7 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B12" s="20">
         <v>45816</v>
@@ -3374,16 +4542,16 @@
         <v>41</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H12" s="13">
         <v>1</v>
@@ -3405,7 +4573,7 @@
     </row>
     <row r="13" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B13" s="16">
         <v>45816</v>
@@ -3414,7 +4582,7 @@
         <v>41</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>9</v>
@@ -3423,7 +4591,7 @@
         <v>43</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -3437,7 +4605,7 @@
         <v>56</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
@@ -3447,7 +4615,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B14" s="20">
         <v>45813</v>
@@ -3456,16 +4624,16 @@
         <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
@@ -3487,7 +4655,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B15" s="16">
         <v>45813</v>
@@ -3496,16 +4664,16 @@
         <v>8</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
@@ -3527,7 +4695,7 @@
     </row>
     <row r="16" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B16" s="20">
         <v>45814</v>
@@ -3536,16 +4704,16 @@
         <v>17</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H16" s="13">
         <v>1</v>
@@ -3567,7 +4735,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B17" s="16">
         <v>45814</v>
@@ -3576,16 +4744,16 @@
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -3607,7 +4775,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B18" s="20">
         <v>45814</v>
@@ -3616,16 +4784,16 @@
         <v>17</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
@@ -3647,7 +4815,7 @@
     </row>
     <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B19" s="16">
         <v>45814</v>
@@ -3656,16 +4824,16 @@
         <v>17</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -3687,7 +4855,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B20" s="20">
         <v>45815</v>
@@ -3696,16 +4864,16 @@
         <v>26</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
@@ -3727,7 +4895,7 @@
     </row>
     <row r="21" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B21" s="16">
         <v>45815</v>
@@ -3736,16 +4904,16 @@
         <v>26</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -3767,7 +4935,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B22" s="20">
         <v>45815</v>
@@ -3776,16 +4944,16 @@
         <v>26</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
@@ -3807,7 +4975,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B23" s="16">
         <v>45815</v>
@@ -3816,16 +4984,16 @@
         <v>26</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -3847,7 +5015,7 @@
     </row>
     <row r="24" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B24" s="20">
         <v>45816</v>
@@ -3856,16 +5024,16 @@
         <v>41</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
@@ -3887,7 +5055,7 @@
     </row>
     <row r="25" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B25" s="16">
         <v>45816</v>
@@ -3896,16 +5064,16 @@
         <v>41</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -3919,7 +5087,7 @@
         <v>55</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
@@ -3957,7 +5125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C31188C-F456-4136-8385-513CC5E1FF62}">
   <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4017,7 +5185,7 @@
     </row>
     <row r="2" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="20">
         <v>45449</v>
@@ -4026,16 +5194,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
@@ -4050,7 +5218,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H12)*2</f>
@@ -4071,7 +5239,7 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" s="16">
         <v>45449</v>
@@ -4080,16 +5248,16 @@
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -4104,7 +5272,7 @@
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H13:H21)*2</f>
@@ -4125,7 +5293,7 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="20">
         <v>45450</v>
@@ -4134,16 +5302,16 @@
         <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -4158,7 +5326,7 @@
       </c>
       <c r="M4" s="13"/>
       <c r="N4" s="22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O4" s="13">
         <f>SUM(H22:H33)*2</f>
@@ -4179,7 +5347,7 @@
     </row>
     <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5" s="16">
         <v>45450</v>
@@ -4188,16 +5356,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
@@ -4219,7 +5387,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B6" s="20">
         <v>45450</v>
@@ -4228,16 +5396,16 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -4271,7 +5439,7 @@
     </row>
     <row r="7" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B7" s="16">
         <v>45450</v>
@@ -4280,16 +5448,16 @@
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
@@ -4311,7 +5479,7 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B8" s="20">
         <v>45450</v>
@@ -4320,16 +5488,16 @@
         <v>26</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -4351,7 +5519,7 @@
     </row>
     <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="16">
         <v>45450</v>
@@ -4360,16 +5528,16 @@
         <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -4391,7 +5559,7 @@
     </row>
     <row r="10" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="20">
         <v>45450</v>
@@ -4400,16 +5568,16 @@
         <v>26</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
@@ -4431,7 +5599,7 @@
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" s="16">
         <v>45450</v>
@@ -4440,16 +5608,16 @@
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H11" s="8">
         <v>1</v>
@@ -4471,7 +5639,7 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="20">
         <v>45450</v>
@@ -4480,16 +5648,16 @@
         <v>41</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H12" s="13">
         <v>1</v>
@@ -4503,7 +5671,7 @@
         <v>60</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -4513,7 +5681,7 @@
     </row>
     <row r="13" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" s="16">
         <v>45449</v>
@@ -4522,16 +5690,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -4553,7 +5721,7 @@
     </row>
     <row r="14" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B14" s="20">
         <v>45450</v>
@@ -4562,16 +5730,16 @@
         <v>17</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
@@ -4593,7 +5761,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="16">
         <v>45450</v>
@@ -4602,16 +5770,16 @@
         <v>17</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>
@@ -4633,7 +5801,7 @@
     </row>
     <row r="16" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="20">
         <v>45450</v>
@@ -4642,16 +5810,16 @@
         <v>17</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H16" s="13">
         <v>1</v>
@@ -4673,7 +5841,7 @@
     </row>
     <row r="17" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="16">
         <v>45451</v>
@@ -4682,16 +5850,16 @@
         <v>26</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H17" s="8">
         <v>1</v>
@@ -4713,7 +5881,7 @@
     </row>
     <row r="18" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="20">
         <v>45451</v>
@@ -4722,16 +5890,16 @@
         <v>26</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H18" s="13">
         <v>1</v>
@@ -4753,7 +5921,7 @@
     </row>
     <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="16">
         <v>45451</v>
@@ -4762,16 +5930,16 @@
         <v>26</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4793,7 +5961,7 @@
     </row>
     <row r="20" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B20" s="20">
         <v>45452</v>
@@ -4802,16 +5970,16 @@
         <v>41</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H20" s="13">
         <v>1</v>
@@ -4833,7 +6001,7 @@
     </row>
     <row r="21" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B21" s="16">
         <v>45452</v>
@@ -4842,16 +6010,16 @@
         <v>41</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H21" s="8">
         <v>1</v>
@@ -4865,7 +6033,7 @@
         <v>60</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -4875,7 +6043,7 @@
     </row>
     <row r="22" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" s="20">
         <v>45449</v>
@@ -4884,16 +6052,16 @@
         <v>8</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>244</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
@@ -4915,7 +6083,7 @@
     </row>
     <row r="23" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" s="16">
         <v>45449</v>
@@ -4924,16 +6092,16 @@
         <v>8</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H23" s="8">
         <v>1</v>
@@ -4955,7 +6123,7 @@
     </row>
     <row r="24" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B24" s="20">
         <v>45450</v>
@@ -4964,16 +6132,16 @@
         <v>17</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
@@ -4995,7 +6163,7 @@
     </row>
     <row r="25" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B25" s="16">
         <v>45450</v>
@@ -5004,16 +6172,16 @@
         <v>17</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H25" s="8">
         <v>1</v>
@@ -5035,7 +6203,7 @@
     </row>
     <row r="26" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B26" s="20">
         <v>45450</v>
@@ -5044,16 +6212,16 @@
         <v>17</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H26" s="13">
         <v>1</v>
@@ -5075,7 +6243,7 @@
     </row>
     <row r="27" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B27" s="16">
         <v>45450</v>
@@ -5084,16 +6252,16 @@
         <v>17</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H27" s="8">
         <v>1</v>
@@ -5115,7 +6283,7 @@
     </row>
     <row r="28" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B28" s="20">
         <v>45451</v>
@@ -5124,16 +6292,16 @@
         <v>26</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H28" s="13">
         <v>1</v>
@@ -5155,7 +6323,7 @@
     </row>
     <row r="29" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B29" s="16">
         <v>45451</v>
@@ -5164,16 +6332,16 @@
         <v>26</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
@@ -5195,7 +6363,7 @@
     </row>
     <row r="30" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B30" s="20">
         <v>45451</v>
@@ -5204,16 +6372,16 @@
         <v>26</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13"/>
@@ -5235,7 +6403,7 @@
     </row>
     <row r="31" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B31" s="16">
         <v>45451</v>
@@ -5244,16 +6412,16 @@
         <v>26</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>11</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -5275,7 +6443,7 @@
     </row>
     <row r="32" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B32" s="20">
         <v>45452</v>
@@ -5284,16 +6452,16 @@
         <v>41</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H32" s="13">
         <v>1</v>
@@ -5315,7 +6483,7 @@
     </row>
     <row r="33" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B33" s="16">
         <v>45452</v>
@@ -5324,16 +6492,16 @@
         <v>41</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H33" s="8">
         <v>1</v>
@@ -5347,7 +6515,7 @@
         <v>63</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
@@ -5361,7 +6529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E51B9D6B-2CD1-40A2-98B7-3DFF5850DB8B}">
   <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5421,7 +6589,7 @@
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="20">
         <v>45085</v>
@@ -5430,16 +6598,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H2" s="13">
         <v>1</v>
@@ -5454,7 +6622,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H12)*2</f>
@@ -5475,7 +6643,7 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" s="16">
         <v>45085</v>
@@ -5484,16 +6652,16 @@
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -5508,7 +6676,7 @@
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H13:H23)*2</f>
@@ -5529,7 +6697,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="20">
         <v>45086</v>
@@ -5538,7 +6706,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>9</v>
@@ -5547,7 +6715,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -5569,7 +6737,7 @@
     </row>
     <row r="5" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5" s="16">
         <v>45086</v>
@@ -5578,16 +6746,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
@@ -5621,7 +6789,7 @@
     </row>
     <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B6" s="20">
         <v>45086</v>
@@ -5630,16 +6798,16 @@
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -5661,7 +6829,7 @@
     </row>
     <row r="7" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B7" s="16">
         <v>45087</v>
@@ -5670,16 +6838,16 @@
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -5701,7 +6869,7 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B8" s="20">
         <v>45087</v>
@@ -5710,16 +6878,16 @@
         <v>26</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -5741,7 +6909,7 @@
     </row>
     <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="16">
         <v>45087</v>
@@ -5750,16 +6918,16 @@
         <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
@@ -5781,7 +6949,7 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="20">
         <v>45087</v>
@@ -5790,16 +6958,16 @@
         <v>26</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H10" s="13">
         <v>1</v>
@@ -5821,7 +6989,7 @@
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" s="16">
         <v>45088</v>
@@ -5830,16 +6998,16 @@
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>183</v>
       </c>
       <c r="H11" s="8">
         <v>1</v>
@@ -5861,7 +7029,7 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="20">
         <v>45088</v>
@@ -5870,16 +7038,16 @@
         <v>41</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H12" s="13">
         <v>1</v>
@@ -5893,7 +7061,7 @@
         <v>55</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -5903,7 +7071,7 @@
     </row>
     <row r="13" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" s="16">
         <v>45085</v>
@@ -5912,16 +7080,16 @@
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -5943,7 +7111,7 @@
     </row>
     <row r="14" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B14" s="20">
         <v>45085</v>
@@ -5952,16 +7120,16 @@
         <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
@@ -5983,7 +7151,7 @@
     </row>
     <row r="15" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="16">
         <v>45086</v>
@@ -5992,16 +7160,16 @@
         <v>17</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>
@@ -6023,7 +7191,7 @@
     </row>
     <row r="16" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="20">
         <v>45086</v>
@@ -6032,16 +7200,16 @@
         <v>17</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H16" s="13">
         <v>1</v>
@@ -6063,7 +7231,7 @@
     </row>
     <row r="17" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="16">
         <v>45086</v>
@@ -6072,16 +7240,16 @@
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -6103,7 +7271,7 @@
     </row>
     <row r="18" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="20">
         <v>45087</v>
@@ -6112,16 +7280,16 @@
         <v>26</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
@@ -6143,7 +7311,7 @@
     </row>
     <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="16">
         <v>45087</v>
@@ -6152,16 +7320,16 @@
         <v>26</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -6183,7 +7351,7 @@
     </row>
     <row r="20" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B20" s="20">
         <v>45087</v>
@@ -6192,16 +7360,16 @@
         <v>26</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
@@ -6223,7 +7391,7 @@
     </row>
     <row r="21" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B21" s="16">
         <v>45087</v>
@@ -6232,16 +7400,16 @@
         <v>26</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -6263,7 +7431,7 @@
     </row>
     <row r="22" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B22" s="20">
         <v>45088</v>
@@ -6272,16 +7440,16 @@
         <v>41</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="13"/>
@@ -6303,7 +7471,7 @@
     </row>
     <row r="23" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B23" s="16">
         <v>45088</v>
@@ -6312,16 +7480,16 @@
         <v>41</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -6335,7 +7503,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
@@ -6349,7 +7517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160DCF80-7DE2-4017-AE5D-F1CF64C0EEA1}">
   <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6409,25 +7577,25 @@
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
@@ -6442,7 +7610,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H12)*2</f>
@@ -6463,25 +7631,25 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -6496,7 +7664,7 @@
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H13:H23)*2</f>
@@ -6517,25 +7685,25 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -6557,25 +7725,25 @@
     </row>
     <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
@@ -6590,7 +7758,7 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O5" s="8">
         <f>SUM(O2:O3)</f>
@@ -6611,25 +7779,25 @@
     </row>
     <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -6651,25 +7819,25 @@
     </row>
     <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
@@ -6691,25 +7859,25 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -6731,25 +7899,25 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -6771,25 +7939,25 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
@@ -6811,25 +7979,25 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -6851,25 +8019,25 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H12" s="13">
         <v>1</v>
@@ -6883,7 +8051,7 @@
         <v>56</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -6893,25 +8061,25 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
@@ -6933,25 +8101,25 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H14" s="13">
         <v>1</v>
@@ -6973,25 +8141,25 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H15" s="8">
         <v>1</v>
@@ -7013,25 +8181,25 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H16" s="13">
         <v>1</v>
@@ -7053,25 +8221,25 @@
     </row>
     <row r="17" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
@@ -7093,25 +8261,25 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
@@ -7131,25 +8299,25 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H19" s="8">
         <v>1</v>
@@ -7171,25 +8339,25 @@
     </row>
     <row r="20" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H20" s="13">
         <v>1</v>
@@ -7211,25 +8379,25 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -7251,25 +8419,25 @@
     </row>
     <row r="22" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H22" s="13">
         <v>1</v>
@@ -7291,25 +8459,25 @@
     </row>
     <row r="23" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -7323,7 +8491,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
@@ -7337,7 +8505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750738BA-4006-4CC7-8943-C96044524BB0}">
   <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7397,25 +8565,25 @@
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>78</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>79</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="13">
         <v>1</v>
@@ -7430,7 +8598,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H12)*2</f>
@@ -7451,25 +8619,25 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -7484,7 +8652,7 @@
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H13:H23)*2</f>
@@ -7505,16 +8673,16 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>21</v>
@@ -7523,7 +8691,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -7545,25 +8713,25 @@
     </row>
     <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
@@ -7578,7 +8746,7 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O5" s="8">
         <f>SUM(O2:O3)</f>
@@ -7599,25 +8767,25 @@
     </row>
     <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -7639,25 +8807,25 @@
     </row>
     <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
@@ -7679,25 +8847,25 @@
     </row>
     <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -7719,25 +8887,25 @@
     </row>
     <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
@@ -7759,25 +8927,25 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H10" s="13">
         <v>1</v>
@@ -7799,25 +8967,25 @@
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -7839,25 +9007,25 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" s="13">
         <v>1</v>
@@ -7871,7 +9039,7 @@
         <v>52</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -7881,25 +9049,25 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
@@ -7921,16 +9089,16 @@
     </row>
     <row r="14" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>21</v>
@@ -7939,7 +9107,7 @@
         <v>43</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="13">
         <v>1</v>
@@ -7961,25 +9129,25 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
@@ -8001,25 +9169,25 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H16" s="13">
         <v>1</v>
@@ -8041,25 +9209,25 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H17" s="8">
         <v>1</v>
@@ -8081,16 +9249,16 @@
     </row>
     <row r="18" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>21</v>
@@ -8099,7 +9267,7 @@
         <v>43</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H18" s="13">
         <v>1</v>
@@ -8121,25 +9289,25 @@
     </row>
     <row r="19" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -8161,25 +9329,25 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H20" s="13">
         <v>1</v>
@@ -8201,25 +9369,25 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>11</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -8241,16 +9409,16 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>42</v>
@@ -8259,7 +9427,7 @@
         <v>14</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H22" s="13">
         <v>1</v>
@@ -8281,16 +9449,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>21</v>
@@ -8299,7 +9467,7 @@
         <v>14</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H23" s="8">
         <v>1</v>
@@ -8313,7 +9481,7 @@
         <v>40</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
@@ -8327,7 +9495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4EF9D9-D70C-4E61-9477-A0F40CBD656F}">
   <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8418,7 +9586,7 @@
       </c>
       <c r="M2" s="13"/>
       <c r="N2" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H12)*2</f>
@@ -8451,13 +9619,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
@@ -8482,7 +9650,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>17</v>
@@ -8491,13 +9659,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="13">
         <v>1</v>
@@ -8522,7 +9690,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>17</v>
@@ -8531,13 +9699,13 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -8562,7 +9730,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>17</v>
@@ -8571,13 +9739,13 @@
         <v>9</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -8602,7 +9770,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>17</v>
@@ -8611,13 +9779,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
@@ -8642,7 +9810,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>26</v>
@@ -8651,13 +9819,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H8" s="13">
         <v>1</v>
@@ -8682,7 +9850,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>26</v>
@@ -8691,13 +9859,13 @@
         <v>9</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
@@ -8719,10 +9887,10 @@
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>26</v>
@@ -8731,13 +9899,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
@@ -8759,10 +9927,10 @@
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>41</v>
@@ -8771,13 +9939,13 @@
         <v>9</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H11" s="8">
         <v>1</v>
@@ -8799,10 +9967,10 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>41</v>
@@ -8811,13 +9979,13 @@
         <v>9</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
@@ -8831,7 +9999,7 @@
         <v>55</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -8844,7 +10012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F90403D-DAD6-4E16-B331-BCE3878C1B19}">
   <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8935,7 +10103,7 @@
       </c>
       <c r="M2" s="31"/>
       <c r="N2" s="32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O2" s="31">
         <f>SUM(H2:H12)*2</f>
@@ -9360,482 +10528,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A76EE42-D30F-444C-A57D-B2E37EAE4ABE}">
-  <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="18" width="10.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="11">
-        <v>2</v>
-      </c>
-      <c r="I1" s="11">
-        <v>1</v>
-      </c>
-      <c r="J1" s="11">
-        <v>0</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B2" s="38">
-        <v>42894</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="H2" s="13">
-        <v>1</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13">
-        <v>54</v>
-      </c>
-      <c r="L2" s="13">
-        <v>54</v>
-      </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="O2" s="13">
-        <f>SUM(H2:H11)*2</f>
-        <v>12</v>
-      </c>
-      <c r="P2" s="13">
-        <f>SUM(J2:J11)*2</f>
-        <v>8</v>
-      </c>
-      <c r="Q2" s="13">
-        <f>SUM(K2:K11)</f>
-        <v>501</v>
-      </c>
-      <c r="R2" s="13">
-        <f>SUM(L2:L11)</f>
-        <v>486</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B3" s="37">
-        <v>42894</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8">
-        <v>32</v>
-      </c>
-      <c r="L3" s="8">
-        <v>50</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-    </row>
-    <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B4" s="38">
-        <v>42895</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
-        <v>1</v>
-      </c>
-      <c r="K4" s="13">
-        <v>40</v>
-      </c>
-      <c r="L4" s="13">
-        <v>50</v>
-      </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-    </row>
-    <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" s="37">
-        <v>42895</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8">
-        <v>51</v>
-      </c>
-      <c r="L5" s="8">
-        <v>38</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-    </row>
-    <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="38">
-        <v>42895</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="H6" s="13">
-        <v>1</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13">
-        <v>50</v>
-      </c>
-      <c r="L6" s="13">
-        <v>43</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-    </row>
-    <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="37">
-        <v>42896</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8">
-        <v>50</v>
-      </c>
-      <c r="L7" s="8">
-        <v>36</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B8" s="38">
-        <v>42896</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13">
-        <v>1</v>
-      </c>
-      <c r="K8" s="13">
-        <v>54</v>
-      </c>
-      <c r="L8" s="13">
-        <v>62</v>
-      </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-    </row>
-    <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B9" s="37">
-        <v>42896</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8">
-        <v>54</v>
-      </c>
-      <c r="L9" s="8">
-        <v>55</v>
-      </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="B10" s="38">
-        <v>42897</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="H10" s="13">
-        <v>1</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13">
-        <v>61</v>
-      </c>
-      <c r="L10" s="13">
-        <v>49</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-    </row>
-    <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B11" s="37">
-        <v>42897</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="H11" s="8">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8">
-        <v>55</v>
-      </c>
-      <c r="L11" s="8">
-        <v>49</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/powercup.xlsx
+++ b/powercup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F30824-CD21-4939-B044-C820EC22F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E937F32-29BB-43DF-ABF8-116446EA6934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
+    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" activeTab="1" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
   </bookViews>
   <sheets>
     <sheet name="powercup" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="362">
   <si>
     <t>sarja</t>
   </si>
@@ -3476,10 +3476,18 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="A2" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" s="20">
+        <v>46184</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E2" s="13"/>
       <c r="F2" s="21"/>
       <c r="G2" s="13"/>
@@ -3510,10 +3518,18 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" s="16">
+        <v>46184</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E3" s="8"/>
       <c r="F3" s="17"/>
       <c r="G3" s="8"/>
@@ -3544,10 +3560,18 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
+      <c r="A4" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B4" s="20">
+        <v>46185</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E4" s="13"/>
       <c r="F4" s="21"/>
       <c r="G4" s="13"/>
@@ -3564,10 +3588,18 @@
       <c r="R4" s="13"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46185</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="17"/>
       <c r="G5" s="8"/>
@@ -3598,10 +3630,18 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
+      <c r="A6" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="20">
+        <v>46185</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E6" s="13"/>
       <c r="F6" s="21"/>
       <c r="G6" s="13"/>
@@ -3618,10 +3658,18 @@
       <c r="R6" s="13"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" s="16">
+        <v>46185</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="17"/>
       <c r="G7" s="8"/>
@@ -3638,10 +3686,18 @@
       <c r="R7" s="8"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
+      <c r="A8" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="20">
+        <v>46186</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E8" s="13"/>
       <c r="F8" s="21"/>
       <c r="G8" s="13"/>
@@ -3658,10 +3714,18 @@
       <c r="R8" s="13"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" s="16">
+        <v>46186</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="17"/>
       <c r="G9" s="8"/>
@@ -3678,10 +3742,18 @@
       <c r="R9" s="8"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
+      <c r="A10" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="20">
+        <v>46186</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E10" s="13"/>
       <c r="F10" s="21"/>
       <c r="G10" s="13"/>
@@ -3698,10 +3770,18 @@
       <c r="R10" s="13"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" s="16">
+        <v>46186</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="17"/>
       <c r="G11" s="8"/>
@@ -3718,10 +3798,18 @@
       <c r="R11" s="8"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
+      <c r="A12" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="20">
+        <v>46187</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>9</v>
+      </c>
       <c r="E12" s="13"/>
       <c r="F12" s="21"/>
       <c r="G12" s="13"/>
@@ -3738,10 +3826,18 @@
       <c r="R12" s="13"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B13" s="16">
+        <v>46187</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="17"/>
       <c r="G13" s="8"/>
@@ -3760,10 +3856,18 @@
       <c r="R13" s="8"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="A14" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B14" s="20">
+        <v>46186</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="E14" s="13"/>
       <c r="F14" s="21"/>
       <c r="G14" s="13"/>
@@ -3780,10 +3884,18 @@
       <c r="R14" s="13"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="A15" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="16">
+        <v>45821</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="17"/>
       <c r="G15" s="8"/>
@@ -3800,10 +3912,18 @@
       <c r="R15" s="8"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+      <c r="A16" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B16" s="20">
+        <v>46186</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="E16" s="13"/>
       <c r="F16" s="21"/>
       <c r="G16" s="13"/>
@@ -3820,10 +3940,18 @@
       <c r="R16" s="13"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="B17" s="16">
+        <v>45821</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="E17" s="8"/>
       <c r="F17" s="17"/>
       <c r="G17" s="8"/>
@@ -3840,10 +3968,18 @@
       <c r="R17" s="8"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
+      <c r="A18" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B18" s="20">
+        <v>46187</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="E18" s="13"/>
       <c r="F18" s="21"/>
       <c r="G18" s="13"/>
@@ -3860,10 +3996,18 @@
       <c r="R18" s="13"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="B19" s="16">
+        <v>45822</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="E19" s="8"/>
       <c r="F19" s="17"/>
       <c r="G19" s="8"/>

--- a/powercup.xlsx
+++ b/powercup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E937F32-29BB-43DF-ABF8-116446EA6934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB1A040-CB57-43BA-A758-80B5CC614858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" activeTab="1" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
+    <workbookView xWindow="264" yWindow="864" windowWidth="22608" windowHeight="12816" activeTab="1" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
   </bookViews>
   <sheets>
     <sheet name="powercup" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="366">
   <si>
     <t>sarja</t>
   </si>
@@ -1132,6 +1132,18 @@
   </si>
   <si>
     <t>B-super/Kajastus/I-V</t>
+  </si>
+  <si>
+    <t>Salpis</t>
+  </si>
+  <si>
+    <t>BV</t>
+  </si>
+  <si>
+    <t>OsVa2</t>
+  </si>
+  <si>
+    <t>PuMa AB</t>
   </si>
 </sst>
 </file>
@@ -3488,7 +3500,9 @@
       <c r="D2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="F2" s="21"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
@@ -3530,7 +3544,9 @@
       <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="F3" s="17"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -3572,7 +3588,9 @@
       <c r="D4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="13" t="s">
+        <v>364</v>
+      </c>
       <c r="F4" s="21"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
@@ -3600,7 +3618,9 @@
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="8" t="s">
+        <v>242</v>
+      </c>
       <c r="F5" s="17"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -3642,7 +3662,9 @@
       <c r="D6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="13" t="s">
+        <v>365</v>
+      </c>
       <c r="F6" s="21"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -3670,7 +3692,9 @@
       <c r="D7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="F7" s="17"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -3698,7 +3722,9 @@
       <c r="D8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="F8" s="21"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -3726,7 +3752,9 @@
       <c r="D9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>365</v>
+      </c>
       <c r="F9" s="17"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -3754,7 +3782,9 @@
       <c r="D10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>242</v>
+      </c>
       <c r="F10" s="21"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -3782,7 +3812,9 @@
       <c r="D11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>364</v>
+      </c>
       <c r="F11" s="17"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
@@ -3810,7 +3842,9 @@
       <c r="D12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="F12" s="21"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -3838,7 +3872,9 @@
       <c r="D13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="8" t="s">
+        <v>363</v>
+      </c>
       <c r="F13" s="17"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -3868,7 +3904,9 @@
       <c r="D14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="13" t="s">
+        <v>305</v>
+      </c>
       <c r="F14" s="21"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -3896,7 +3934,9 @@
       <c r="D15" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="8" t="s">
+        <v>362</v>
+      </c>
       <c r="F15" s="17"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
@@ -3924,7 +3964,9 @@
       <c r="D16" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>158</v>
+      </c>
       <c r="F16" s="21"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
@@ -3996,18 +4038,10 @@
       <c r="R18" s="13"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="B19" s="16">
-        <v>45822</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>55</v>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="17"/>
       <c r="G19" s="8"/>

--- a/powercup.xlsx
+++ b/powercup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB1A040-CB57-43BA-A758-80B5CC614858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8F0504-5DDD-4E02-A25F-BE6BA86F37FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="264" yWindow="864" windowWidth="22608" windowHeight="12816" activeTab="1" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
+    <workbookView xWindow="264" yWindow="864" windowWidth="22608" windowHeight="12816" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
   </bookViews>
   <sheets>
     <sheet name="powercup" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="366">
   <si>
     <t>sarja</t>
   </si>
@@ -1821,7 +1821,7 @@
         <v>275</v>
       </c>
       <c r="C2" s="13">
-        <f t="shared" ref="C2:C8" si="0">SUM(D2:F2)</f>
+        <f t="shared" ref="C2:C10" si="0">SUM(D2:F2)</f>
         <v>22</v>
       </c>
       <c r="D2" s="13">
@@ -2078,12 +2078,29 @@
       <c r="B9" s="42" t="s">
         <v>359</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="C9" s="8">
+        <f>SUM(D9:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="43">
+        <f>'2026'!O2/2</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="43">
+        <v>0</v>
+      </c>
+      <c r="F9" s="43">
+        <f>'2026'!P2/2</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="43">
+        <f>'2026'!Q2</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="43">
+        <f>'2026'!R2</f>
+        <v>0</v>
+      </c>
       <c r="I9" s="44"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -2099,12 +2116,29 @@
       <c r="B10" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="C10" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <f>'2026'!O3/2</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <f>'2026'!P3/2</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <f>'2026'!Q3</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <f>'2026'!R3</f>
+        <v>0</v>
+      </c>
       <c r="I10" s="14"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -3559,19 +3593,19 @@
         <v>357</v>
       </c>
       <c r="O3" s="8">
-        <f>SUM(H14:H25)*2</f>
+        <f>SUM(H14:H18)*2</f>
         <v>0</v>
       </c>
       <c r="P3" s="8">
-        <f>SUM(J14:J25)*2</f>
+        <f>SUM(J14:J18)*2</f>
         <v>0</v>
       </c>
       <c r="Q3" s="8">
-        <f>SUM(K14:K25)</f>
+        <f>SUM(K14:K18)</f>
         <v>0</v>
       </c>
       <c r="R3" s="8">
-        <f>SUM(L14:L25)</f>
+        <f>SUM(L14:L18)</f>
         <v>0</v>
       </c>
     </row>
@@ -3882,9 +3916,7 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="8" t="s">
-        <v>298</v>
-      </c>
+      <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -4170,9 +4202,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
-      <c r="M25" s="8" t="s">
-        <v>316</v>
-      </c>
+      <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>

--- a/powercup.xlsx
+++ b/powercup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8F0504-5DDD-4E02-A25F-BE6BA86F37FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC041DB-29F5-4D84-8E19-97E76EB4DEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="264" yWindow="864" windowWidth="22608" windowHeight="12816" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12804" xr2:uid="{872D5EE9-3762-4425-92BE-822A3ECA4638}"/>
   </bookViews>
   <sheets>
     <sheet name="powercup" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="381">
   <si>
     <t>sarja</t>
   </si>
@@ -1144,6 +1144,51 @@
   </si>
   <si>
     <t>PuMa AB</t>
+  </si>
+  <si>
+    <t>25-19,25-23</t>
+  </si>
+  <si>
+    <t>25-21,25-27,6-15</t>
+  </si>
+  <si>
+    <t>25-17,17-25,6-15</t>
+  </si>
+  <si>
+    <t>25-20,25-13</t>
+  </si>
+  <si>
+    <t>25-11,25-20</t>
+  </si>
+  <si>
+    <t>22-25,25-23,15-11</t>
+  </si>
+  <si>
+    <t>25-16,21-25,15-12</t>
+  </si>
+  <si>
+    <t>25-16,25-20</t>
+  </si>
+  <si>
+    <t>25-16,25-12</t>
+  </si>
+  <si>
+    <t>25-14,25-23</t>
+  </si>
+  <si>
+    <t>25-23,18-25,11-15</t>
+  </si>
+  <si>
+    <t>25-18,25-15</t>
+  </si>
+  <si>
+    <t>25-16,25-18</t>
+  </si>
+  <si>
+    <t>26-24,18-25,12-15</t>
+  </si>
+  <si>
+    <t>23-25,24-26</t>
   </si>
 </sst>
 </file>
@@ -2080,28 +2125,30 @@
       </c>
       <c r="C9" s="8">
         <f>SUM(D9:F9)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D9" s="43">
         <f>'2026'!O2/2</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E9" s="43">
         <v>0</v>
       </c>
       <c r="F9" s="43">
         <f>'2026'!P2/2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="43">
         <f>'2026'!Q2</f>
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="H9" s="43">
         <f>'2026'!R2</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="44"/>
+        <v>544</v>
+      </c>
+      <c r="I9" s="44">
+        <v>2</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2118,28 +2165,30 @@
       </c>
       <c r="C10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D10" s="13">
         <f>'2026'!O3/2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
         <f>'2026'!P3/2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="13">
         <f>'2026'!Q3</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="H10" s="13">
         <f>'2026'!R3</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="14"/>
+        <v>219</v>
+      </c>
+      <c r="I10" s="14">
+        <v>4</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2171,11 +2220,11 @@
       <c r="B12" s="13"/>
       <c r="C12" s="12">
         <f t="shared" ref="C12:H12" si="1">SUM(C2:C11)</f>
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="D12" s="12">
         <f t="shared" si="1"/>
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
@@ -2183,15 +2232,15 @@
       </c>
       <c r="F12" s="12">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" si="1"/>
-        <v>7997</v>
+        <v>8881</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>7534</v>
+        <v>8297</v>
       </c>
       <c r="I12" s="13"/>
       <c r="K12" s="1"/>
@@ -3537,35 +3586,45 @@
       <c r="E2" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="F2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="H2" s="13">
+        <v>1</v>
+      </c>
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="K2" s="13">
+        <v>50</v>
+      </c>
+      <c r="L2" s="13">
+        <v>42</v>
+      </c>
       <c r="M2" s="13"/>
       <c r="N2" s="22" t="s">
         <v>356</v>
       </c>
       <c r="O2" s="13">
         <f>SUM(H2:H13)*2</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P2" s="13">
         <f>SUM(J2:J13)*2</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="13">
         <f>SUM(K2:K13)</f>
-        <v>0</v>
+        <v>631</v>
       </c>
       <c r="R2" s="13">
         <f>SUM(L2:L13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>356</v>
       </c>
@@ -3581,35 +3640,45 @@
       <c r="E3" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="F3" s="17"/>
-      <c r="G3" s="8"/>
+      <c r="F3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>367</v>
+      </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="J3" s="8">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8">
+        <v>56</v>
+      </c>
+      <c r="L3" s="8">
+        <v>63</v>
+      </c>
       <c r="M3" s="8"/>
       <c r="N3" s="18" t="s">
         <v>357</v>
       </c>
       <c r="O3" s="8">
         <f>SUM(H14:H18)*2</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P3" s="8">
         <f>SUM(J14:J18)*2</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q3" s="8">
         <f>SUM(K14:K18)</f>
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R3" s="8">
         <f>SUM(L14:L18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>356</v>
       </c>
@@ -3625,13 +3694,23 @@
       <c r="E4" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="13"/>
+      <c r="F4" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>368</v>
+      </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="J4" s="13">
+        <v>1</v>
+      </c>
+      <c r="K4" s="13">
+        <v>48</v>
+      </c>
+      <c r="L4" s="13">
+        <v>57</v>
+      </c>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -3655,32 +3734,42 @@
       <c r="E5" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="F5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="8">
+        <v>50</v>
+      </c>
+      <c r="L5" s="8">
+        <v>33</v>
+      </c>
       <c r="M5" s="8"/>
       <c r="N5" s="18" t="s">
         <v>354</v>
       </c>
       <c r="O5" s="8">
         <f>SUM(O2:O3)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P5" s="8">
         <f>SUM(P2:P3)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="8">
         <f>SUM(Q2:Q3)</f>
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="R5" s="8">
         <f>SUM(R2:R3)</f>
-        <v>0</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -3699,13 +3788,23 @@
       <c r="E6" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="F6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="H6" s="13">
+        <v>1</v>
+      </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
+      <c r="K6" s="13">
+        <v>50</v>
+      </c>
+      <c r="L6" s="13">
+        <v>31</v>
+      </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
       <c r="O6" s="13"/>
@@ -3713,7 +3812,7 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>356</v>
       </c>
@@ -3729,13 +3828,23 @@
       <c r="E7" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="F7" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="K7" s="8">
+        <v>62</v>
+      </c>
+      <c r="L7" s="8">
+        <v>59</v>
+      </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -3743,7 +3852,7 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>356</v>
       </c>
@@ -3759,13 +3868,23 @@
       <c r="E8" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="F8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+      <c r="K8" s="13">
+        <v>61</v>
+      </c>
+      <c r="L8" s="13">
+        <v>53</v>
+      </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13"/>
@@ -3789,13 +3908,23 @@
       <c r="E9" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="F9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="K9" s="8">
+        <v>50</v>
+      </c>
+      <c r="L9" s="8">
+        <v>36</v>
+      </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -3819,13 +3948,23 @@
       <c r="E10" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="F10" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H10" s="13">
+        <v>1</v>
+      </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="K10" s="13">
+        <v>50</v>
+      </c>
+      <c r="L10" s="13">
+        <v>28</v>
+      </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
@@ -3849,13 +3988,23 @@
       <c r="E11" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="F11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
+      <c r="K11" s="8">
+        <v>50</v>
+      </c>
+      <c r="L11" s="8">
+        <v>37</v>
+      </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
@@ -3879,13 +4028,23 @@
       <c r="E12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="F12" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="13">
+        <v>1</v>
+      </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
+      <c r="K12" s="13">
+        <v>50</v>
+      </c>
+      <c r="L12" s="13">
+        <v>42</v>
+      </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
@@ -3893,7 +4052,7 @@
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>356</v>
       </c>
@@ -3909,13 +4068,23 @@
       <c r="E13" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="8"/>
+      <c r="F13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>376</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>54</v>
+      </c>
+      <c r="L13" s="8">
+        <v>63</v>
+      </c>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
       <c r="O13" s="8"/>
@@ -3939,13 +4108,23 @@
       <c r="E14" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
+      <c r="F14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="H14" s="13">
+        <v>1</v>
+      </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
+      <c r="K14" s="13">
+        <v>50</v>
+      </c>
+      <c r="L14" s="13">
+        <v>33</v>
+      </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
@@ -3969,13 +4148,23 @@
       <c r="E15" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="F15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
+      <c r="K15" s="8">
+        <v>50</v>
+      </c>
+      <c r="L15" s="8">
+        <v>34</v>
+      </c>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
@@ -3999,13 +4188,23 @@
       <c r="E16" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="F16" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H16" s="13">
+        <v>1</v>
+      </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+      <c r="K16" s="13">
+        <v>50</v>
+      </c>
+      <c r="L16" s="13">
+        <v>38</v>
+      </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
@@ -4013,7 +4212,7 @@
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>357</v>
       </c>
@@ -4026,14 +4225,26 @@
       <c r="D17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="8"/>
+      <c r="E17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>379</v>
+      </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>56</v>
+      </c>
+      <c r="L17" s="8">
+        <v>63</v>
+      </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
@@ -4054,14 +4265,26 @@
       <c r="D18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>380</v>
+      </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
+      <c r="J18" s="13">
+        <v>1</v>
+      </c>
+      <c r="K18" s="13">
+        <v>47</v>
+      </c>
+      <c r="L18" s="13">
+        <v>51</v>
+      </c>
       <c r="M18" s="13"/>
       <c r="N18" s="13"/>
       <c r="O18" s="13"/>
